--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/post FET_HRM-2031-0300/Panel-28/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/post FET_HRM-2031-0300/Panel-28/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Back_Summary.xlsx
@@ -437,16 +437,6 @@
           <t>Radius</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -460,19 +450,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.81789</v>
+        <v>17.90415</v>
       </c>
       <c r="D2" t="n">
-        <v>17.32788</v>
+        <v>17.83756</v>
       </c>
       <c r="E2" t="n">
-        <v>17.78763</v>
+        <v>17.86433</v>
+      </c>
+      <c r="F2" t="n">
+        <v>46.1627</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05456</v>
+        <v>0.05464</v>
       </c>
       <c r="H2" t="n">
-        <v>1.94334</v>
+        <v>1.91427</v>
       </c>
     </row>
     <row r="3">
@@ -482,22 +475,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18.02526</v>
+        <v>18.04307</v>
       </c>
       <c r="D3" t="n">
-        <v>17.44819</v>
+        <v>17.70779</v>
       </c>
       <c r="E3" t="n">
-        <v>17.62184</v>
+        <v>17.72514</v>
       </c>
       <c r="F3" t="n">
-        <v>45.5331</v>
+        <v>45.89235</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.05264</v>
       </c>
       <c r="H3" t="n">
-        <v>1.91929</v>
+        <v>1.92877</v>
       </c>
     </row>
     <row r="4">
@@ -506,25 +499,23 @@
           <t>Unit 9</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+      <c r="C4" t="n">
+        <v>17.92008</v>
       </c>
       <c r="D4" t="n">
-        <v>17.95909</v>
+        <v>17.58731</v>
       </c>
       <c r="E4" t="n">
-        <v>17.95893</v>
+        <v>17.86018</v>
       </c>
       <c r="F4" t="n">
-        <v>45.43437</v>
+        <v>44.01661</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05386</v>
+        <v>0.0547</v>
       </c>
       <c r="H4" t="n">
-        <v>1.93851</v>
+        <v>1.9125</v>
       </c>
     </row>
     <row r="5">
@@ -533,25 +524,23 @@
           <t>Unit 4</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>12,5</t>
-        </is>
+      <c r="C5" t="n">
+        <v>17.95318</v>
       </c>
       <c r="D5" t="n">
-        <v>17.62794</v>
+        <v>17.58573</v>
       </c>
       <c r="E5" t="n">
-        <v>17.87401</v>
+        <v>17.95123</v>
       </c>
       <c r="F5" t="n">
-        <v>44.76647</v>
+        <v>45.43386</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05389</v>
+        <v>0.05399</v>
       </c>
       <c r="H5" t="n">
-        <v>1.95903</v>
+        <v>1.93229</v>
       </c>
     </row>
     <row r="6">
@@ -561,22 +550,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18.15376</v>
+        <v>17.99064</v>
       </c>
       <c r="D6" t="n">
-        <v>17.70283</v>
+        <v>17.61596</v>
       </c>
       <c r="E6" t="n">
-        <v>17.74689</v>
+        <v>17.9711</v>
       </c>
       <c r="F6" t="n">
-        <v>46.01182</v>
+        <v>44.72613</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05423</v>
-      </c>
-      <c r="H6" t="e">
-        <v>#DIV/0!</v>
+        <v>0.05388</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.93408</v>
       </c>
     </row>
     <row r="7">
@@ -586,24 +575,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>18.03519</v>
+        <v>18.02389</v>
       </c>
       <c r="D7" t="n">
-        <v>17.22876</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 16.48 </t>
-        </is>
+        <v>17.73316</v>
+      </c>
+      <c r="E7" t="n">
+        <v>17.93173</v>
       </c>
       <c r="F7" t="n">
-        <v>45.96017</v>
+        <v>45.31195</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05323</v>
+        <v>0.05373</v>
       </c>
       <c r="H7" t="n">
-        <v>1.94412</v>
+        <v>1.93492</v>
       </c>
     </row>
     <row r="8">
@@ -613,22 +600,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.50738</v>
+        <v>17.82606</v>
       </c>
       <c r="D8" t="n">
-        <v>17.75744</v>
+        <v>17.1294</v>
       </c>
       <c r="E8" t="n">
-        <v>17.63294</v>
+        <v>17.43843</v>
       </c>
       <c r="F8" t="n">
-        <v>45.71838</v>
+        <v>45.24262</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05408</v>
+        <v>0.05255</v>
       </c>
       <c r="H8" t="n">
-        <v>1.93102</v>
+        <v>1.92848</v>
       </c>
     </row>
     <row r="9">
@@ -638,22 +625,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.96473</v>
+        <v>17.80696</v>
       </c>
       <c r="D9" t="n">
-        <v>17.56383</v>
+        <v>17.18332</v>
       </c>
       <c r="E9" t="n">
-        <v>18.0141</v>
+        <v>17.78779</v>
       </c>
       <c r="F9" t="n">
-        <v>44.70481</v>
+        <v>45.72987</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0531</v>
+        <v>0.05475</v>
       </c>
       <c r="H9" t="n">
-        <v>1.92154</v>
+        <v>1.9293</v>
       </c>
     </row>
     <row r="10">
@@ -663,22 +650,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.85836</v>
+        <v>17.71259</v>
       </c>
       <c r="D10" t="n">
-        <v>17.83643</v>
+        <v>17.39186</v>
       </c>
       <c r="E10" t="n">
-        <v>17.30738</v>
+        <v>17.52946</v>
       </c>
       <c r="F10" t="n">
-        <v>45.24125</v>
+        <v>45.48642</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05373</v>
+        <v>0.05401</v>
       </c>
       <c r="H10" t="n">
-        <v>1.93059</v>
+        <v>1.9285</v>
       </c>
     </row>
     <row r="11">
@@ -705,10 +692,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.63519</v>
       </c>
       <c r="D12" t="n">
-        <v>1.16568</v>
+        <v>1.16662</v>
       </c>
     </row>
     <row r="13">
@@ -718,10 +705,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>0.64068</v>
       </c>
       <c r="D13" t="n">
-        <v>1.18785</v>
+        <v>1.16247</v>
       </c>
     </row>
     <row r="14">
@@ -731,10 +718,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.64795</v>
       </c>
       <c r="D14" t="n">
-        <v>1.18502</v>
+        <v>1.14539</v>
       </c>
     </row>
     <row r="15">
@@ -744,10 +731,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.65424</v>
       </c>
       <c r="D15" t="n">
-        <v>1.18662</v>
+        <v>1.18276</v>
       </c>
     </row>
     <row r="16">
@@ -757,10 +744,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.63874</v>
       </c>
       <c r="D16" t="n">
-        <v>1.17298</v>
+        <v>1.18208</v>
       </c>
     </row>
     <row r="17">
@@ -770,10 +757,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.6332100000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>1.17027</v>
+        <v>1.1676</v>
       </c>
     </row>
     <row r="18">
@@ -783,10 +770,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.6402</v>
       </c>
       <c r="D18" t="n">
-        <v>1.18894</v>
+        <v>1.19086</v>
       </c>
     </row>
     <row r="19">
@@ -796,10 +783,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.64635</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1659</v>
+        <v>1.16776</v>
       </c>
     </row>
     <row r="20">
@@ -809,10 +796,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.6401</v>
       </c>
       <c r="D20" t="n">
-        <v>1.18159</v>
+        <v>1.17941</v>
       </c>
     </row>
   </sheetData>
